--- a/06_附件资料/工程类型映射表0610.xlsx
+++ b/06_附件资料/工程类型映射表0610.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13044"/>
+    <workbookView windowWidth="18180" windowHeight="8808"/>
   </bookViews>
   <sheets>
-    <sheet name="固定映射表" sheetId="1" r:id="rId1"/>
+    <sheet name="传值信息" sheetId="2" r:id="rId1"/>
+    <sheet name="工程类型映射表" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,146 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="108">
+  <si>
+    <t>字段</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>投/被保险人名称</t>
+  </si>
+  <si>
+    <t>投/被保险人应相同，小型工程总包/施工单位名称</t>
+  </si>
+  <si>
+    <t>文本</t>
+  </si>
+  <si>
+    <t>证件类型</t>
+  </si>
+  <si>
+    <t>可默认为统一信用代码证，无需合作方传值</t>
+  </si>
+  <si>
+    <t>统一社会信用代码号</t>
+  </si>
+  <si>
+    <t>传号码值，投/被保险人识别编码</t>
+  </si>
+  <si>
+    <t>联系人手机号码</t>
+  </si>
+  <si>
+    <t>请提供用于短信发送</t>
+  </si>
+  <si>
+    <t>联系人邮箱</t>
+  </si>
+  <si>
+    <t>无需合作方传值，用户在投保页面填写</t>
+  </si>
+  <si>
+    <t>工程状态</t>
+  </si>
+  <si>
+    <t>可默认为未开工，无需合作方传值，根据文件要求必须提供保单后进行备案方可开工</t>
+  </si>
+  <si>
+    <t>工程地址</t>
+  </si>
+  <si>
+    <t>合作方传值</t>
+  </si>
+  <si>
+    <t>工程详细地址市/区</t>
+  </si>
+  <si>
+    <t>无需合作方传值、默认为上海省、上海市、青浦区</t>
+  </si>
+  <si>
+    <t>投保工程所在区域</t>
+  </si>
+  <si>
+    <t>无需合作方传值，默认为郊环线外（该字段为原住建安责统保必填项，无关紧要建议取默认值即可）</t>
+  </si>
+  <si>
+    <t>工程类型</t>
+  </si>
+  <si>
+    <t>房屋建筑/建筑装修/市政工程(不含涉水桥梁、地下工程)/园林绿化/房屋修缮/线路管道工程/机电设备安装工程/桥隧占比低于 60%的公路、铁路项目/桥梁、堤坝、码头等涉水作业工程
+合作方需建立码值表提供对应的工程类型</t>
+  </si>
+  <si>
+    <t>合作方需建立码值表提供对应的工程类型</t>
+  </si>
+  <si>
+    <t>工程名称</t>
+  </si>
+  <si>
+    <t>营业性质</t>
+  </si>
+  <si>
+    <t>无需合作方传值，建议默认为房屋建筑业，对承保条件无影响，不显示在电子保单内</t>
+  </si>
+  <si>
+    <t>营业性质名称</t>
+  </si>
+  <si>
+    <t>同上</t>
+  </si>
+  <si>
+    <t>是否投保工伤保险</t>
+  </si>
+  <si>
+    <t>无需合作方传值，默认为否</t>
+  </si>
+  <si>
+    <t>是否分包</t>
+  </si>
+  <si>
+    <t>投保造价</t>
+  </si>
+  <si>
+    <t>数值</t>
+  </si>
+  <si>
+    <t>投保工程概况</t>
+  </si>
+  <si>
+    <t>无需合作方传值，简化默认为“小型工程”</t>
+  </si>
+  <si>
+    <t>工程起期</t>
+  </si>
+  <si>
+    <t>日期</t>
+  </si>
+  <si>
+    <t>工程止期</t>
+  </si>
+  <si>
+    <t>保险起期</t>
+  </si>
+  <si>
+    <t>保险止期</t>
+  </si>
+  <si>
+    <t>营业执照</t>
+  </si>
+  <si>
+    <t>JPG或其他图片格式传输</t>
+  </si>
+  <si>
+    <t>施工合同</t>
+  </si>
+  <si>
+    <t>PDF或其他格式传输</t>
+  </si>
   <si>
     <t>序号</t>
   </si>
@@ -213,9 +353,6 @@
   </si>
   <si>
     <t>其他存在坍塌/物体打击/高处坠落/消防安全/机械伤害等风险的零星作业</t>
-  </si>
-  <si>
-    <t>由于前端采集字段不够，本质上都存在分类较粗的问题，无法依赖额外字段判断细分码值</t>
   </si>
 </sst>
 </file>
@@ -228,7 +365,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -242,6 +379,18 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -589,12 +738,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -698,28 +862,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -728,124 +883,145 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1229,6 +1405,265 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr defaultColWidth="8.8" defaultRowHeight="15.6" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="18.6" customWidth="1"/>
+    <col min="2" max="2" width="88.8" customWidth="1"/>
+    <col min="3" max="3" width="7.9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" ht="72" spans="1:3">
+      <c r="A11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="2"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:H26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <cols>
@@ -1244,25 +1679,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1270,22 +1705,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="G2" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1293,22 +1728,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1316,22 +1751,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="G4" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1339,22 +1774,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="H5" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1362,22 +1797,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="H6" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1385,22 +1820,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="H7" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1408,22 +1843,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="G8" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1431,22 +1866,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="G9" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="H9" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1454,22 +1889,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="G10" t="s">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="H10" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1477,22 +1912,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="G11" t="s">
-        <v>37</v>
+        <v>83</v>
       </c>
       <c r="H11" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1500,22 +1935,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="G12" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="H12" t="s">
-        <v>41</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1523,22 +1958,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="G13" t="s">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="H13" t="s">
-        <v>46</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1546,22 +1981,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="G14" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="H14" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1569,22 +2004,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="E15" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="G15" t="s">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="H15" t="s">
-        <v>52</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1592,16 +2027,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1609,16 +2044,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="E17" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1626,16 +2061,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="E18" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1643,16 +2078,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="C19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D19" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" t="s">
         <v>56</v>
-      </c>
-      <c r="D19" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1660,16 +2095,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="D20" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="E20" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1677,16 +2112,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="E21" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1694,16 +2129,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="E22" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1711,16 +2146,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>60</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="E23" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1728,28 +2163,26 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>61</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="E24" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="1" t="s">
-        <v>62</v>
-      </c>
+      <c r="A26" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:A2 D1:E1 C2:E2 A3:E24" numberStoredAsText="1"/>
+    <ignoredError sqref="A3:E24 C2:E2 D1:E1 A1:A2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>